--- a/fix/298-identity-reliability-mandatory/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/fix/298-identity-reliability-mandatory/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T12:37:34+00:00</t>
+    <t>2026-10-07T07:07:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
